--- a/NEA-Walk-Forward-Test.xlsx
+++ b/NEA-Walk-Forward-Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dd266ef2451b5a0b/Documents/Finance/strat-opt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{45E5EA45-39DD-4C37-91BD-D468C0607F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5EF6B67-FB8E-4B62-95F3-AE70200BDD2A}"/>
+  <xr:revisionPtr revIDLastSave="268" documentId="8_{45E5EA45-39DD-4C37-91BD-D468C0607F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60160987-DD3D-4E49-80B1-41B21109FFF3}"/>
   <bookViews>
-    <workbookView xWindow="560" yWindow="6280" windowWidth="25180" windowHeight="15260" xr2:uid="{DEEFBD0B-CC45-4DFE-926A-F4D952ED301A}"/>
+    <workbookView xWindow="460" yWindow="3320" windowWidth="25180" windowHeight="15260" xr2:uid="{DEEFBD0B-CC45-4DFE-926A-F4D952ED301A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="32">
   <si>
     <t>Range</t>
   </si>
@@ -53,57 +53,6 @@
     <t>2003-2007</t>
   </si>
   <si>
-    <t>2004-2008</t>
-  </si>
-  <si>
-    <t>2005-2009</t>
-  </si>
-  <si>
-    <t>2006-2010</t>
-  </si>
-  <si>
-    <t>2007-2011</t>
-  </si>
-  <si>
-    <t>2008-2012</t>
-  </si>
-  <si>
-    <t>2009-2013</t>
-  </si>
-  <si>
-    <t>2010-2014</t>
-  </si>
-  <si>
-    <t>2011-2015</t>
-  </si>
-  <si>
-    <t>2012-2016</t>
-  </si>
-  <si>
-    <t>2013-2017</t>
-  </si>
-  <si>
-    <t>2014-2018</t>
-  </si>
-  <si>
-    <t>2015-2019</t>
-  </si>
-  <si>
-    <t>2016-2020</t>
-  </si>
-  <si>
-    <t>2017-2021</t>
-  </si>
-  <si>
-    <t>2018-2022</t>
-  </si>
-  <si>
-    <t>2019-2023</t>
-  </si>
-  <si>
-    <t>2020-2024</t>
-  </si>
-  <si>
     <t>chg4</t>
   </si>
   <si>
@@ -132,6 +81,57 @@
   </si>
   <si>
     <t>d 10</t>
+  </si>
+  <si>
+    <t>2003-2008</t>
+  </si>
+  <si>
+    <t>2003-2009</t>
+  </si>
+  <si>
+    <t>2003-2010</t>
+  </si>
+  <si>
+    <t>2003-2011</t>
+  </si>
+  <si>
+    <t>2003-2012</t>
+  </si>
+  <si>
+    <t>2003-2013</t>
+  </si>
+  <si>
+    <t>2003-2014</t>
+  </si>
+  <si>
+    <t>2003-2015</t>
+  </si>
+  <si>
+    <t>2003-2016</t>
+  </si>
+  <si>
+    <t>2003-2017</t>
+  </si>
+  <si>
+    <t>2003-2018</t>
+  </si>
+  <si>
+    <t>2003-2019</t>
+  </si>
+  <si>
+    <t>2003-2020</t>
+  </si>
+  <si>
+    <t>2003-2021</t>
+  </si>
+  <si>
+    <t>2003-2022</t>
+  </si>
+  <si>
+    <t>2003-2023</t>
+  </si>
+  <si>
+    <t>2003-2024</t>
   </si>
 </sst>
 </file>
@@ -186,6 +186,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -522,31 +526,31 @@
         <v>3</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="G1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="H1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="I1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="J1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K1" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>1</v>
@@ -566,7 +570,7 @@
         <v>0.32500000000000001</v>
       </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E2">
         <v>0.01</v>
@@ -578,16 +582,16 @@
         <v>0.26</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="J2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="L2" s="2">
         <v>-0.25940000000000002</v>
@@ -598,189 +602,699 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B3">
         <v>2009</v>
       </c>
+      <c r="C3">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3">
+        <v>0.04</v>
+      </c>
+      <c r="F3">
+        <v>0.01</v>
+      </c>
+      <c r="G3">
+        <v>0.26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
       <c r="L3" s="2">
         <v>0.34649999999999997</v>
       </c>
+      <c r="M3" s="2">
+        <v>0.37380000000000002</v>
+      </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B4">
         <v>2010</v>
       </c>
+      <c r="C4">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>0.06</v>
+      </c>
+      <c r="G4">
+        <v>0.26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" t="s">
+        <v>10</v>
+      </c>
       <c r="L4" s="2">
         <v>1.5E-3</v>
       </c>
+      <c r="M4" s="2">
+        <v>4.4600000000000001E-2</v>
+      </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B5">
         <v>2011</v>
       </c>
+      <c r="C5">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>0.06</v>
+      </c>
+      <c r="G5">
+        <v>0.26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K5" t="s">
+        <v>10</v>
+      </c>
       <c r="L5" s="2">
         <v>0.18970000000000001</v>
       </c>
+      <c r="M5" s="2">
+        <v>0.13830000000000001</v>
+      </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B6">
         <v>2012</v>
       </c>
+      <c r="C6">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>0.06</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" t="s">
+        <v>10</v>
+      </c>
       <c r="L6" s="2">
         <v>8.1000000000000003E-2</v>
       </c>
+      <c r="M6" s="2">
+        <v>9.5399999999999999E-2</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>2013</v>
       </c>
+      <c r="C7">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>0.06</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" t="s">
+        <v>10</v>
+      </c>
       <c r="L7" s="2">
         <v>-0.17630000000000001</v>
       </c>
+      <c r="M7" s="2">
+        <v>-0.1072</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B8">
         <v>2014</v>
       </c>
+      <c r="C8">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D8" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>0.04</v>
+      </c>
+      <c r="F8">
+        <v>0.08</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
       <c r="L8" s="2">
         <v>0.2072</v>
       </c>
+      <c r="M8" s="2">
+        <v>0.17499999999999999</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B9">
         <v>2015</v>
       </c>
+      <c r="C9">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>0.01</v>
+      </c>
+      <c r="F9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I9">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J9" t="s">
+        <v>10</v>
+      </c>
+      <c r="K9" t="s">
+        <v>10</v>
+      </c>
       <c r="L9" s="2">
         <v>6.2899999999999998E-2</v>
       </c>
+      <c r="M9" s="2">
+        <v>6.6500000000000004E-2</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B10">
         <v>2016</v>
       </c>
+      <c r="C10">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>0.01</v>
+      </c>
+      <c r="F10">
+        <v>0.1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J10" t="s">
+        <v>10</v>
+      </c>
+      <c r="K10" t="s">
+        <v>10</v>
+      </c>
       <c r="L10" s="2">
         <v>8.3000000000000001E-3</v>
       </c>
+      <c r="M10" s="2">
+        <v>2.3900000000000001E-2</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B11">
         <v>2017</v>
       </c>
+      <c r="C11">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>0.01</v>
+      </c>
+      <c r="F11">
+        <v>0.1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" t="s">
+        <v>10</v>
+      </c>
       <c r="L11" s="2">
         <v>8.9700000000000002E-2</v>
       </c>
+      <c r="M11" s="2">
+        <v>2.86E-2</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B12">
         <v>2018</v>
       </c>
+      <c r="C12">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>0.01</v>
+      </c>
+      <c r="F12">
+        <v>0.1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J12" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" t="s">
+        <v>10</v>
+      </c>
       <c r="L12" s="2">
         <v>-6.3899999999999998E-2</v>
       </c>
+      <c r="M12" s="2">
+        <v>-2.46E-2</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B13">
         <v>2019</v>
       </c>
+      <c r="C13">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>1E-3</v>
+      </c>
+      <c r="F13">
+        <v>0.1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s">
+        <v>10</v>
+      </c>
+      <c r="I13">
+        <v>2.4E-2</v>
+      </c>
+      <c r="J13" t="s">
+        <v>10</v>
+      </c>
+      <c r="K13" t="s">
+        <v>10</v>
+      </c>
       <c r="L13" s="2">
         <v>0.20069999999999999</v>
       </c>
+      <c r="M13" s="2">
+        <v>4.4299999999999999E-2</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B14">
         <v>2020</v>
       </c>
+      <c r="C14">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>0.06</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s">
+        <v>10</v>
+      </c>
+      <c r="I14" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" t="s">
+        <v>10</v>
+      </c>
       <c r="L14" s="2">
         <v>0.1008</v>
       </c>
+      <c r="M14" s="2">
+        <v>0.1527</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>2021</v>
       </c>
+      <c r="C15">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>0.06</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s">
+        <v>10</v>
+      </c>
+      <c r="I15" t="s">
+        <v>10</v>
+      </c>
+      <c r="J15" t="s">
+        <v>10</v>
+      </c>
+      <c r="K15" t="s">
+        <v>10</v>
+      </c>
       <c r="L15" s="2">
         <v>9.0999999999999998E-2</v>
       </c>
+      <c r="M15" s="2">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B16">
         <v>2022</v>
       </c>
+      <c r="C16">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s">
+        <v>10</v>
+      </c>
+      <c r="I16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" t="s">
+        <v>10</v>
+      </c>
       <c r="L16" s="2">
         <v>-0.21129999999999999</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M16" s="2">
+        <v>-4.2500000000000003E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="B17">
         <v>2023</v>
       </c>
+      <c r="C17">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>0.06</v>
+      </c>
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I17" t="s">
+        <v>10</v>
+      </c>
+      <c r="J17" t="s">
+        <v>10</v>
+      </c>
+      <c r="K17" t="s">
+        <v>10</v>
+      </c>
       <c r="L17" s="2">
         <v>1.8499999999999999E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M17" s="2">
+        <v>6.3200000000000006E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B18">
         <v>2024</v>
       </c>
+      <c r="C18">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D18" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>0.01</v>
+      </c>
+      <c r="F18">
+        <v>0.1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s">
+        <v>10</v>
+      </c>
+      <c r="I18" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" t="s">
+        <v>10</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
       <c r="L18" s="2">
         <v>8.0299999999999996E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M18" s="2">
+        <v>4.1099999999999998E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B19">
         <v>2025</v>
       </c>
+      <c r="C19">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19">
+        <v>0.04</v>
+      </c>
+      <c r="F19">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" t="s">
+        <v>10</v>
+      </c>
+      <c r="J19" t="s">
+        <v>10</v>
+      </c>
+      <c r="K19">
+        <v>1</v>
+      </c>
       <c r="L19" s="2">
         <v>9.1300000000000006E-2</v>
+      </c>
+      <c r="M19" s="2">
+        <v>0.1105</v>
       </c>
     </row>
   </sheetData>
